--- a/산출물/PostgreSQL_인덱스_설계서_Running_Coach_v2.0.xlsx
+++ b/산출물/PostgreSQL_인덱스_설계서_Running_Coach_v2.0.xlsx
@@ -2,24 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="516" yWindow="576" windowWidth="21792" windowHeight="9732" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인덱스설계서" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -27,13 +26,24 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -45,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B365D"/>
-        <bgColor rgb="001B365D"/>
+        <fgColor rgb="FF1B365D"/>
+        <bgColor rgb="FF1B365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9FAFB"/>
-        <bgColor rgb="00F9FAFB"/>
+        <fgColor rgb="FFF9FAFB"/>
+        <bgColor rgb="FFF9FAFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,23 +76,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,9 +110,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -464,15 +479,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" style="7" min="1" max="1"/>
+    <col width="24" customWidth="1" style="7" min="2" max="2"/>
+    <col width="32" customWidth="1" style="7" min="3" max="3"/>
+    <col width="14" customWidth="1" style="7" min="4" max="4"/>
+    <col width="32" customWidth="1" style="7" min="5" max="5"/>
+    <col width="60" customWidth="1" style="7" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -747,7 +762,128 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>GARMIN_RUN_DETAIL</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>UIDX_GARMIN_RUN_DETAIL_01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>garmin_activity_id</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>가민 원본 Activity ID 중복 방지 및 1:1 고속 조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>GARMIN_RUN_DETAIL</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>UIDX_GARMIN_RUN_DETAIL_02</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>run_record_id</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>메인 러닝 기록(RUN_RECORD) 기준 1:1 상세 조인 성능 최적화</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>GARMIN_RUN_LAP</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>IDX_GARMIN_RUN_LAP_01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Non-Unique</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>run_record_id, lap_index</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>러닝 기록별 km 구간(랩 타임) 순차 조회 및 정렬 최적화</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GARMIN_ACCOUNT_LINK</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IDX_GARMIN_LINK_01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Non-Unique</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>is_connected, last_synced_at</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>백그라운드 스케줄러의 연동 대상 유저 검색 및 증분 동기화 속도 최적화</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>